--- a/SpaceX_xAI_Financial_Model.xlsx
+++ b/SpaceX_xAI_Financial_Model.xlsx
@@ -19,6 +19,7 @@
     <sheet name="xAI Valuation &amp; Sensitivity" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Dilution &amp; Share Count" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Assumptions &amp; Notes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SpaceX Competitive &amp; Margins" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -121,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -178,6 +179,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3104,7 +3117,7 @@
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Model generated: 2026-02-08 03:56 UTC</t>
+          <t>Model generated: 2026-05-18 02:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3118,6 +3131,4408 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F3864"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H169"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SpaceX — Competitive Landscape &amp; Segment Margin Analysis</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1. LAUNCH SERVICES — COMPETITIVE POSITIONING</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SpaceX (Falcon 9/Heavy)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>ULA (Vulcan)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Arianespace (Ariane 6)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Rocket Lab (Neutron)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Blue Origin (New Glenn)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>China (Long March)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Price to LEO ($/kg)</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>$2,700</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>$15,000 - $20,000</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>$12,000 - $15,000</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>$5,500 (est.)</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>$8,000 (est.)</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>$4,000 - $8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Price to GTO ($M, full)</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>$67M</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>$110 - $150M</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>$90 - $115M</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>$55M (est.)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>$80M (est.)</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>$60 - $70M</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Reusability</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Booster: 20+ flights</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Expendable</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Expendable</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>Planned (booster)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>Planned (booster)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>Expendable</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Payload to LEO (kg)</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>22,800</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>27,200</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>21,650</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>45,000</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>25,000 (CZ-5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2024 Launch Cadence</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>134 (actual)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>15 (Electron)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>0 (development)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2025E Launch Cadence</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>~155</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>~10</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>~8</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>~18 + Neutron test</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>~3-5</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>~75</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Manifest Backlog ($B)</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>&gt;$5B</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>~$3B (NatSec)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>~$2B</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>&lt;$1B</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>~$2B (Kuiper)</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>n/a (state)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Key Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Cost + cadence + reliability</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>NatSec assured access</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>EU sovereignty</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>Smallsat niche</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>Payload capacity</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>State subsidy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Key Vulnerability</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Regulatory / concentration</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Cost structure</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Delayed timeline</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>Scale limitations</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>Unproven</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>Geopolitical risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>LAUNCH SERVICES — MARGIN EXPECTATIONS</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2022A</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2023A</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2024A</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2025E</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Long-Term Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Segment Revenue ($M)</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n">
+        <v>2928</v>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>4410</v>
+      </c>
+      <c r="D17" s="23" t="n">
+        <v>5896</v>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>6665</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>7140</v>
+      </c>
+      <c r="G17" s="23" t="n">
+        <v>7770</v>
+      </c>
+      <c r="H17" s="23" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Launch Revenue</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="n">
+        <v>2928</v>
+      </c>
+      <c r="C18" s="23" t="n">
+        <v>4410</v>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>5896</v>
+      </c>
+      <c r="E18" s="23" t="n">
+        <v>6665</v>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>7140</v>
+      </c>
+      <c r="G18" s="23" t="n">
+        <v>7770</v>
+      </c>
+      <c r="H18" s="23" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Segment COGS ($M)</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="n">
+        <v>1318</v>
+      </c>
+      <c r="C19" s="23" t="n">
+        <v>1764</v>
+      </c>
+      <c r="D19" s="23" t="n">
+        <v>2358</v>
+      </c>
+      <c r="E19" s="23" t="n">
+        <v>2533</v>
+      </c>
+      <c r="F19" s="23" t="n">
+        <v>2570</v>
+      </c>
+      <c r="G19" s="23" t="n">
+        <v>2720</v>
+      </c>
+      <c r="H19" s="23" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Propellant &amp; consumables</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>220</v>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>330</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>350</v>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>370</v>
+      </c>
+      <c r="H20" s="23" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Refurbishment &amp; recovery</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="C21" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="D21" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="E21" s="23" t="n">
+        <v>480</v>
+      </c>
+      <c r="F21" s="23" t="n">
+        <v>460</v>
+      </c>
+      <c r="G21" s="23" t="n">
+        <v>440</v>
+      </c>
+      <c r="H21" s="23" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Manufacturing (fairings, 2nd stage)</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="C22" s="23" t="n">
+        <v>700</v>
+      </c>
+      <c r="D22" s="23" t="n">
+        <v>900</v>
+      </c>
+      <c r="E22" s="23" t="n">
+        <v>950</v>
+      </c>
+      <c r="F22" s="23" t="n">
+        <v>950</v>
+      </c>
+      <c r="G22" s="23" t="n">
+        <v>960</v>
+      </c>
+      <c r="H22" s="23" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Launch operations &amp; range fees</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>280</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>380</v>
+      </c>
+      <c r="E23" s="23" t="n">
+        <v>430</v>
+      </c>
+      <c r="F23" s="23" t="n">
+        <v>460</v>
+      </c>
+      <c r="G23" s="23" t="n">
+        <v>490</v>
+      </c>
+      <c r="H23" s="23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Insurance &amp; other</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="n">
+        <v>168</v>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>164</v>
+      </c>
+      <c r="D24" s="23" t="n">
+        <v>278</v>
+      </c>
+      <c r="E24" s="23" t="n">
+        <v>343</v>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>350</v>
+      </c>
+      <c r="G24" s="23" t="n">
+        <v>460</v>
+      </c>
+      <c r="H24" s="23" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Segment Gross Profit ($M)</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>1610</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>2646</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>3538</v>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>4132</v>
+      </c>
+      <c r="F25" s="25" t="n">
+        <v>4570</v>
+      </c>
+      <c r="G25" s="25" t="n">
+        <v>5050</v>
+      </c>
+      <c r="H25" s="25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Segment Gross Margin %</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G26" s="25" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="inlineStr">
+        <is>
+          <t>68-72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="23" t="inlineStr"/>
+      <c r="C27" s="23" t="inlineStr"/>
+      <c r="D27" s="23" t="inlineStr"/>
+      <c r="E27" s="23" t="inlineStr"/>
+      <c r="F27" s="23" t="inlineStr"/>
+      <c r="G27" s="23" t="inlineStr"/>
+      <c r="H27" s="23" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Margin Drivers:</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr"/>
+      <c r="C28" s="23" t="inlineStr"/>
+      <c r="D28" s="23" t="inlineStr"/>
+      <c r="E28" s="23" t="inlineStr"/>
+      <c r="F28" s="23" t="inlineStr"/>
+      <c r="G28" s="23" t="inlineStr"/>
+      <c r="H28" s="23" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Booster reuse (avg flights/booster)</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="E29" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="F29" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="G29" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>30+</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fairing reuse rate</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fixed-cost leverage (launches/pad)</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C31" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="D31" s="23" t="n">
+        <v>40</v>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>45</v>
+      </c>
+      <c r="F31" s="23" t="n">
+        <v>48</v>
+      </c>
+      <c r="G31" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Internal vs. external mix</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>30% int.</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>35% int.</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>40% int.</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>42% int.</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>45% int.</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>48% int.</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>50%+</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>Thesis: SpaceX launch margins expand as reuse amortizes fixed manufacturing costs across more flights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>Moat = cadence (reliability track record → insurance discounts) + cost (reuse) + capacity (only provider with &gt;100 annual launches).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2. STARLINK — COMPETITIVE POSITIONING</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SpaceX (Starlink)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Amazon (Kuiper)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>OneWeb (Eutelsat)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Telesat (Lightspeed)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Viasat (GEO+LEO)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Traditional Telcos (fiber/4G)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Constellation Size (2025E)</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>6,500+ operational</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>0 (first launch 2025)</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>650 satellites</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>~300 (planned)</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>3 GEO + LEO planned</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>n/a (terrestrial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Subscribers (2024)</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>4.5M</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>~200K (est.)</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>~800K</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Price ($/month)</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>$120 (US)</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>TBD (~$100 est.)</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>$50-80 (B2B focus)</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>B2B only</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>$100-200</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr">
+        <is>
+          <t>$50-80 (fiber)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Download Speed (Mbps)</t>
+        </is>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>50-250</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>Target: 100-400</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>40-80</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>Target: 100+</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>25-100</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>100-1,000 (fiber)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Latency (ms)</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>20-40</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>Target: &lt;30</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>40-70</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
+        <is>
+          <t>Target: &lt;50</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>600+ (GEO)</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>5-20 (fiber)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Capex Invested ($B)</t>
+        </is>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>&gt;$10B cumulative</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>$10B+ committed</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>~$3B</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>~$5B</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>~$4B</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>varies</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Launch Cost Advantage</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>Internal (~$15M/launch)</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>Blue Origin dependency</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>3rd party ($50M+)</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>3rd party</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>3rd party</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Coverage (% land mass)</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>~60-70%</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>0% (pre-launch)</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>~40%</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>~50%</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>~30% (fiber)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Key Differentiator</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>Scale + vertical integration</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>AWS bundle + capital</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>Govt contracts</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>Enterprise focus</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>Installed base</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>Low latency</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Key Risk</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>Spectrum congestion, ARPU dilution</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>Execution delay</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>Capital constraints</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>Technology age</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
+        <is>
+          <t>Rural economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>STARLINK — MARGIN EXPECTATIONS</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n"/>
+      <c r="C50" s="3" t="n"/>
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="n"/>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>2022A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>2023A</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>2024A</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>2025E</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Long-Term Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Segment Revenue ($M)</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="n">
+        <v>831</v>
+      </c>
+      <c r="C52" s="23" t="n">
+        <v>2678</v>
+      </c>
+      <c r="D52" s="23" t="n">
+        <v>5022</v>
+      </c>
+      <c r="E52" s="23" t="n">
+        <v>7560</v>
+      </c>
+      <c r="F52" s="23" t="n">
+        <v>10440</v>
+      </c>
+      <c r="G52" s="23" t="n">
+        <v>13770</v>
+      </c>
+      <c r="H52" s="23" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Consumer residential</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="n">
+        <v>700</v>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D53" s="23" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E53" s="23" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F53" s="23" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G53" s="23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H53" s="23" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Business / Maritime / Aviation</t>
+        </is>
+      </c>
+      <c r="B54" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C54" s="23" t="n">
+        <v>350</v>
+      </c>
+      <c r="D54" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="E54" s="23" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F54" s="23" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G54" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H54" s="23" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Government / Starshield</t>
+        </is>
+      </c>
+      <c r="B55" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="C55" s="23" t="n">
+        <v>128</v>
+      </c>
+      <c r="D55" s="23" t="n">
+        <v>222</v>
+      </c>
+      <c r="E55" s="23" t="n">
+        <v>360</v>
+      </c>
+      <c r="F55" s="23" t="n">
+        <v>540</v>
+      </c>
+      <c r="G55" s="23" t="n">
+        <v>770</v>
+      </c>
+      <c r="H55" s="23" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Segment COGS ($M)</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="n">
+        <v>581</v>
+      </c>
+      <c r="C56" s="23" t="n">
+        <v>1607</v>
+      </c>
+      <c r="D56" s="23" t="n">
+        <v>2511</v>
+      </c>
+      <c r="E56" s="23" t="n">
+        <v>3326</v>
+      </c>
+      <c r="F56" s="23" t="n">
+        <v>4176</v>
+      </c>
+      <c r="G56" s="23" t="n">
+        <v>5094</v>
+      </c>
+      <c r="H56" s="23" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Satellite manufacturing &amp; launch</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="C57" s="23" t="n">
+        <v>600</v>
+      </c>
+      <c r="D57" s="23" t="n">
+        <v>900</v>
+      </c>
+      <c r="E57" s="23" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F57" s="23" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G57" s="23" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H57" s="23" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  User terminal (CPE) subsidy</t>
+        </is>
+      </c>
+      <c r="B58" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="C58" s="23" t="n">
+        <v>600</v>
+      </c>
+      <c r="D58" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="E58" s="23" t="n">
+        <v>900</v>
+      </c>
+      <c r="F58" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G58" s="23" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H58" s="23" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ground station &amp; network ops</t>
+        </is>
+      </c>
+      <c r="B59" s="23" t="n">
+        <v>80</v>
+      </c>
+      <c r="C59" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="D59" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="E59" s="23" t="n">
+        <v>600</v>
+      </c>
+      <c r="F59" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="G59" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H59" s="23" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Spectrum &amp; licensing fees</t>
+        </is>
+      </c>
+      <c r="B60" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="C60" s="23" t="n">
+        <v>107</v>
+      </c>
+      <c r="D60" s="23" t="n">
+        <v>211</v>
+      </c>
+      <c r="E60" s="23" t="n">
+        <v>326</v>
+      </c>
+      <c r="F60" s="23" t="n">
+        <v>476</v>
+      </c>
+      <c r="G60" s="23" t="n">
+        <v>694</v>
+      </c>
+      <c r="H60" s="23" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Customer support &amp; logistics</t>
+        </is>
+      </c>
+      <c r="B61" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C61" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D61" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="E61" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="F61" s="23" t="n">
+        <v>600</v>
+      </c>
+      <c r="G61" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="H61" s="23" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>Segment Gross Profit ($M)</t>
+        </is>
+      </c>
+      <c r="B62" s="25" t="n">
+        <v>250</v>
+      </c>
+      <c r="C62" s="25" t="n">
+        <v>1071</v>
+      </c>
+      <c r="D62" s="25" t="n">
+        <v>2511</v>
+      </c>
+      <c r="E62" s="25" t="n">
+        <v>4234</v>
+      </c>
+      <c r="F62" s="25" t="n">
+        <v>6264</v>
+      </c>
+      <c r="G62" s="25" t="n">
+        <v>8676</v>
+      </c>
+      <c r="H62" s="25" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>Segment Gross Margin %</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="D63" s="25" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="F63" s="25" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G63" s="25" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="H63" s="25" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr"/>
+      <c r="B64" s="23" t="inlineStr"/>
+      <c r="C64" s="23" t="inlineStr"/>
+      <c r="D64" s="23" t="inlineStr"/>
+      <c r="E64" s="23" t="inlineStr"/>
+      <c r="F64" s="23" t="inlineStr"/>
+      <c r="G64" s="23" t="inlineStr"/>
+      <c r="H64" s="23" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Margin Drivers:</t>
+        </is>
+      </c>
+      <c r="B65" s="23" t="inlineStr"/>
+      <c r="C65" s="23" t="inlineStr"/>
+      <c r="D65" s="23" t="inlineStr"/>
+      <c r="E65" s="23" t="inlineStr"/>
+      <c r="F65" s="23" t="inlineStr"/>
+      <c r="G65" s="23" t="inlineStr"/>
+      <c r="H65" s="23" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CPE cost per terminal</t>
+        </is>
+      </c>
+      <c r="B66" s="23" t="inlineStr">
+        <is>
+          <t>$1,300</t>
+        </is>
+      </c>
+      <c r="C66" s="23" t="inlineStr">
+        <is>
+          <t>$800</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="inlineStr">
+        <is>
+          <t>$500</t>
+        </is>
+      </c>
+      <c r="E66" s="23" t="inlineStr">
+        <is>
+          <t>$400</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>$350</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr">
+        <is>
+          <t>$300</t>
+        </is>
+      </c>
+      <c r="H66" s="23" t="inlineStr">
+        <is>
+          <t>$200</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CPE sale price</t>
+        </is>
+      </c>
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>$599</t>
+        </is>
+      </c>
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>$599</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="inlineStr">
+        <is>
+          <t>$599</t>
+        </is>
+      </c>
+      <c r="E67" s="23" t="inlineStr">
+        <is>
+          <t>$599</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>$599</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr">
+        <is>
+          <t>$599</t>
+        </is>
+      </c>
+      <c r="H67" s="23" t="inlineStr">
+        <is>
+          <t>$499</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CPE subsidy per unit</t>
+        </is>
+      </c>
+      <c r="B68" s="23" t="inlineStr">
+        <is>
+          <t>($701)</t>
+        </is>
+      </c>
+      <c r="C68" s="23" t="inlineStr">
+        <is>
+          <t>($201)</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="inlineStr">
+        <is>
+          <t>$99</t>
+        </is>
+      </c>
+      <c r="E68" s="23" t="inlineStr">
+        <is>
+          <t>$199</t>
+        </is>
+      </c>
+      <c r="F68" s="23" t="inlineStr">
+        <is>
+          <t>$249</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr">
+        <is>
+          <t>$299</t>
+        </is>
+      </c>
+      <c r="H68" s="23" t="inlineStr">
+        <is>
+          <t>$299</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sat manufacturing cost (Gen2)</t>
+        </is>
+      </c>
+      <c r="B69" s="23" t="inlineStr">
+        <is>
+          <t>$500K</t>
+        </is>
+      </c>
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>$400K</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="inlineStr">
+        <is>
+          <t>$300K</t>
+        </is>
+      </c>
+      <c r="E69" s="23" t="inlineStr">
+        <is>
+          <t>$250K</t>
+        </is>
+      </c>
+      <c r="F69" s="23" t="inlineStr">
+        <is>
+          <t>$220K</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr">
+        <is>
+          <t>$200K</t>
+        </is>
+      </c>
+      <c r="H69" s="23" t="inlineStr">
+        <is>
+          <t>$150K</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sat lifespan (years)</t>
+        </is>
+      </c>
+      <c r="B70" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D70" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" s="23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F70" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G70" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H70" s="23" t="inlineStr">
+        <is>
+          <t>7+</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sats per launch (Starlink)</t>
+        </is>
+      </c>
+      <c r="B71" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C71" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="D71" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="E71" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="F71" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="G71" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" s="23" t="inlineStr">
+        <is>
+          <t>40+ (Starship)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Internal launch cost allocation</t>
+        </is>
+      </c>
+      <c r="B72" s="23" t="inlineStr">
+        <is>
+          <t>$15M</t>
+        </is>
+      </c>
+      <c r="C72" s="23" t="inlineStr">
+        <is>
+          <t>$15M</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="inlineStr">
+        <is>
+          <t>$15M</t>
+        </is>
+      </c>
+      <c r="E72" s="23" t="inlineStr">
+        <is>
+          <t>$14M</t>
+        </is>
+      </c>
+      <c r="F72" s="23" t="inlineStr">
+        <is>
+          <t>$12M</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr">
+        <is>
+          <t>$10M</t>
+        </is>
+      </c>
+      <c r="H72" s="23" t="inlineStr">
+        <is>
+          <t>$5M (Starship)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Revenue / sat / year ($K)</t>
+        </is>
+      </c>
+      <c r="B73" s="23" t="n">
+        <v>130</v>
+      </c>
+      <c r="C73" s="23" t="n">
+        <v>380</v>
+      </c>
+      <c r="D73" s="23" t="n">
+        <v>770</v>
+      </c>
+      <c r="E73" s="23" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F73" s="23" t="n">
+        <v>1044</v>
+      </c>
+      <c r="G73" s="23" t="n">
+        <v>1377</v>
+      </c>
+      <c r="H73" s="23" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="26" t="inlineStr">
+        <is>
+          <t>Thesis: Starlink margins expand rapidly as CPE subsidy disappears (2024+), sat costs decline, and Starship slashes launch costs per sat by ~80%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="26" t="inlineStr">
+        <is>
+          <t>Risk: Amazon Kuiper launches 2025-2026 with $10B+ war chest; could pressure pricing in key markets. However, SpaceX has 3-4 year head start and vertical integration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>3. STARSHIP — COMPETITIVE POSITIONING</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n"/>
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SpaceX (Starship)</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Blue Origin (New Glenn)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>ULA (Vulcan Heavy)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>NASA SLS</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>China (CZ-9)</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Relativity (Terran R)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Payload to LEO (kg)</t>
+        </is>
+      </c>
+      <c r="B80" s="23" t="inlineStr">
+        <is>
+          <t>100,000 - 150,000</t>
+        </is>
+      </c>
+      <c r="C80" s="23" t="inlineStr">
+        <is>
+          <t>45,000</t>
+        </is>
+      </c>
+      <c r="D80" s="23" t="inlineStr">
+        <is>
+          <t>27,200</t>
+        </is>
+      </c>
+      <c r="E80" s="23" t="inlineStr">
+        <is>
+          <t>95,000 (Block 1)</t>
+        </is>
+      </c>
+      <c r="F80" s="23" t="inlineStr">
+        <is>
+          <t>150,000 (planned)</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Payload to GTO (kg)</t>
+        </is>
+      </c>
+      <c r="B81" s="23" t="inlineStr">
+        <is>
+          <t>~21,000 (expendable)</t>
+        </is>
+      </c>
+      <c r="C81" s="23" t="inlineStr">
+        <is>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="D81" s="23" t="inlineStr">
+        <is>
+          <t>10,060</t>
+        </is>
+      </c>
+      <c r="E81" s="23" t="inlineStr">
+        <is>
+          <t>n/a (crew)</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>50,000 (planned)</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Target Cost / Launch</t>
+        </is>
+      </c>
+      <c r="B82" s="23" t="inlineStr">
+        <is>
+          <t>$10-50M (reusable)</t>
+        </is>
+      </c>
+      <c r="C82" s="23" t="inlineStr">
+        <is>
+          <t>$80-100M (partial reuse)</t>
+        </is>
+      </c>
+      <c r="D82" s="23" t="inlineStr">
+        <is>
+          <t>$110-150M</t>
+        </is>
+      </c>
+      <c r="E82" s="23" t="inlineStr">
+        <is>
+          <t>$2.2B (per launch)</t>
+        </is>
+      </c>
+      <c r="F82" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr">
+        <is>
+          <t>$55M (target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Target Cost / kg to LEO</t>
+        </is>
+      </c>
+      <c r="B83" s="23" t="inlineStr">
+        <is>
+          <t>$10-50</t>
+        </is>
+      </c>
+      <c r="C83" s="23" t="inlineStr">
+        <is>
+          <t>$2,000-3,000</t>
+        </is>
+      </c>
+      <c r="D83" s="23" t="inlineStr">
+        <is>
+          <t>$5,500-8,000</t>
+        </is>
+      </c>
+      <c r="E83" s="23" t="inlineStr">
+        <is>
+          <t>$23,000</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr">
+        <is>
+          <t>$2,750</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Reusability</t>
+        </is>
+      </c>
+      <c r="B84" s="23" t="inlineStr">
+        <is>
+          <t>Fully reusable (both stages)</t>
+        </is>
+      </c>
+      <c r="C84" s="23" t="inlineStr">
+        <is>
+          <t>Booster only</t>
+        </is>
+      </c>
+      <c r="D84" s="23" t="inlineStr">
+        <is>
+          <t>Expendable</t>
+        </is>
+      </c>
+      <c r="E84" s="23" t="inlineStr">
+        <is>
+          <t>Expendable (SRBs reuse planned)</t>
+        </is>
+      </c>
+      <c r="F84" s="23" t="inlineStr">
+        <is>
+          <t>Planned partial</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>First Orbital Flight</t>
+        </is>
+      </c>
+      <c r="B85" s="23" t="inlineStr">
+        <is>
+          <t>2024 (test)</t>
+        </is>
+      </c>
+      <c r="C85" s="23" t="inlineStr">
+        <is>
+          <t>2025 (target)</t>
+        </is>
+      </c>
+      <c r="D85" s="23" t="inlineStr">
+        <is>
+          <t>2024 (achieved)</t>
+        </is>
+      </c>
+      <c r="E85" s="23" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>2030 (target)</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr">
+        <is>
+          <t>2026+ (target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Revenue Contracts Secured</t>
+        </is>
+      </c>
+      <c r="B86" s="23" t="inlineStr">
+        <is>
+          <t>NASA HLS $4B, DOD, commercial</t>
+        </is>
+      </c>
+      <c r="C86" s="23" t="inlineStr">
+        <is>
+          <t>NASA, Kuiper</t>
+        </is>
+      </c>
+      <c r="D86" s="23" t="inlineStr">
+        <is>
+          <t>DOD NSSL Phase 2</t>
+        </is>
+      </c>
+      <c r="E86" s="23" t="inlineStr">
+        <is>
+          <t>NASA Artemis only</t>
+        </is>
+      </c>
+      <c r="F86" s="23" t="inlineStr">
+        <is>
+          <t>State program</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr">
+        <is>
+          <t>Minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Key Advantage</t>
+        </is>
+      </c>
+      <c r="B87" s="23" t="inlineStr">
+        <is>
+          <t>Full reuse + mass to orbit</t>
+        </is>
+      </c>
+      <c r="C87" s="23" t="inlineStr">
+        <is>
+          <t>Orbital reef / Kuiper synergy</t>
+        </is>
+      </c>
+      <c r="D87" s="23" t="inlineStr">
+        <is>
+          <t>NatSec track record</t>
+        </is>
+      </c>
+      <c r="E87" s="23" t="inlineStr">
+        <is>
+          <t>Crew-rated, deep space</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>State backing</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t>3D printing</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Status (2025)</t>
+        </is>
+      </c>
+      <c r="B88" s="23" t="inlineStr">
+        <is>
+          <t>Iterating toward operational</t>
+        </is>
+      </c>
+      <c r="C88" s="23" t="inlineStr">
+        <is>
+          <t>Pre-first-flight</t>
+        </is>
+      </c>
+      <c r="D88" s="23" t="inlineStr">
+        <is>
+          <t>Early operations</t>
+        </is>
+      </c>
+      <c r="E88" s="23" t="inlineStr">
+        <is>
+          <t>Artemis II pending</t>
+        </is>
+      </c>
+      <c r="F88" s="23" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>STARSHIP — MARGIN EXPECTATIONS (nascent, highly uncertain)</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n"/>
+      <c r="C90" s="3" t="n"/>
+      <c r="D90" s="3" t="n"/>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="n"/>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>2022A</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>2023A</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>2024A</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>2025E</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Long-Term Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Segment Revenue ($M)</t>
+        </is>
+      </c>
+      <c r="B92" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="E92" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="F92" s="23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G92" s="23" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H92" s="23" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NASA HLS milestones</t>
+        </is>
+      </c>
+      <c r="B93" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="E93" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="F93" s="23" t="n">
+        <v>600</v>
+      </c>
+      <c r="G93" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="H93" s="23" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DOD / NatSec contracts</t>
+        </is>
+      </c>
+      <c r="B94" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="E94" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="F94" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="G94" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="H94" s="23" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Commercial (sat deployment)</t>
+        </is>
+      </c>
+      <c r="B95" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="F95" s="23" t="n">
+        <v>600</v>
+      </c>
+      <c r="G95" s="23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H95" s="23" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Point-to-point / cargo</t>
+        </is>
+      </c>
+      <c r="B96" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G96" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="H96" s="23" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Internal (Starlink v3 deployment)</t>
+        </is>
+      </c>
+      <c r="B97" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E97" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F97" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="G97" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="H97" s="23" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Segment COGS ($M)</t>
+        </is>
+      </c>
+      <c r="B98" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="E98" s="23" t="n">
+        <v>640</v>
+      </c>
+      <c r="F98" s="23" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G98" s="23" t="n">
+        <v>2100</v>
+      </c>
+      <c r="H98" s="23" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Vehicle manufacturing</t>
+        </is>
+      </c>
+      <c r="B99" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E99" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="F99" s="23" t="n">
+        <v>600</v>
+      </c>
+      <c r="G99" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="H99" s="23" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Propellant &amp; ops</t>
+        </is>
+      </c>
+      <c r="B100" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="E100" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F100" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="G100" s="23" t="n">
+        <v>350</v>
+      </c>
+      <c r="H100" s="23" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ground infrastructure</t>
+        </is>
+      </c>
+      <c r="B101" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="E101" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="F101" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="G101" s="23" t="n">
+        <v>450</v>
+      </c>
+      <c r="H101" s="23" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  R&amp;D amortization</t>
+        </is>
+      </c>
+      <c r="B102" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="E102" s="23" t="n">
+        <v>90</v>
+      </c>
+      <c r="F102" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="G102" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="H102" s="23" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="24" t="inlineStr">
+        <is>
+          <t>Segment Gross Profit ($M)</t>
+        </is>
+      </c>
+      <c r="B103" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="25" t="n">
+        <v>160</v>
+      </c>
+      <c r="F103" s="25" t="n">
+        <v>600</v>
+      </c>
+      <c r="G103" s="25" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H103" s="25" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="24" t="inlineStr">
+        <is>
+          <t>Segment Gross Margin %</t>
+        </is>
+      </c>
+      <c r="B104" s="25" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C104" s="25" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D104" s="25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E104" s="25" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F104" s="25" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G104" s="25" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="H104" s="25" t="inlineStr">
+        <is>
+          <t>60-70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr"/>
+      <c r="B105" s="23" t="inlineStr"/>
+      <c r="C105" s="23" t="inlineStr"/>
+      <c r="D105" s="23" t="inlineStr"/>
+      <c r="E105" s="23" t="inlineStr"/>
+      <c r="F105" s="23" t="inlineStr"/>
+      <c r="G105" s="23" t="inlineStr"/>
+      <c r="H105" s="23" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>Margin Drivers:</t>
+        </is>
+      </c>
+      <c r="B106" s="23" t="inlineStr"/>
+      <c r="C106" s="23" t="inlineStr"/>
+      <c r="D106" s="23" t="inlineStr"/>
+      <c r="E106" s="23" t="inlineStr"/>
+      <c r="F106" s="23" t="inlineStr"/>
+      <c r="G106" s="23" t="inlineStr"/>
+      <c r="H106" s="23" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Flights per Starship vehicle (target)</t>
+        </is>
+      </c>
+      <c r="B107" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C107" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D107" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F107" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G107" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H107" s="23" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Manufacturing cost / vehicle ($M)</t>
+        </is>
+      </c>
+      <c r="B108" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C108" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D108" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="E108" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="F108" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G108" s="23" t="n">
+        <v>80</v>
+      </c>
+      <c r="H108" s="23" t="inlineStr">
+        <is>
+          <t>30-50</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cost per flight at reuse target ($M)</t>
+        </is>
+      </c>
+      <c r="B109" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C109" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D109" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="E109" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="F109" s="23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G109" s="23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H109" s="23" t="inlineStr">
+        <is>
+          <t>~$2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Revenue per flight ($M)</t>
+        </is>
+      </c>
+      <c r="B110" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C110" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D110" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="E110" s="23" t="n">
+        <v>267</v>
+      </c>
+      <c r="F110" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="G110" s="23" t="n">
+        <v>233</v>
+      </c>
+      <c r="H110" s="23" t="inlineStr">
+        <is>
+          <t>varies</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="26" t="inlineStr">
+        <is>
+          <t>Thesis: Starship is the most disruptive margin story — if full reuse works at cadence, cost/kg drops 100x vs. Falcon 9, creating a new market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="26" t="inlineStr">
+        <is>
+          <t>Bull case: airline-like economics (vehicle flies daily, marginal cost = propellant + ops). Bear case: reliability issues delay full reuse, margins stay thin through 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>4. GOVERNMENT &amp; OTHER (Dragon, ISS, NatSec) — COMPETITIVE POSITIONING</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n"/>
+      <c r="C115" s="3" t="n"/>
+      <c r="D115" s="3" t="n"/>
+      <c r="E115" s="3" t="n"/>
+      <c r="F115" s="3" t="n"/>
+      <c r="G115" s="3" t="n"/>
+      <c r="H115" s="3" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>SpaceX (Dragon/Crew)</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Boeing (Starliner)</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Sierra Space (Dream Chaser)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Northrop (Cygnus)</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Axiom Space</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>International (Soyuz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Crew Capacity</t>
+        </is>
+      </c>
+      <c r="B117" s="23" t="inlineStr">
+        <is>
+          <t>4-7 astronauts</t>
+        </is>
+      </c>
+      <c r="C117" s="23" t="inlineStr">
+        <is>
+          <t>4-7 astronauts</t>
+        </is>
+      </c>
+      <c r="D117" s="23" t="inlineStr">
+        <is>
+          <t>7 crew (planned)</t>
+        </is>
+      </c>
+      <c r="E117" s="23" t="inlineStr">
+        <is>
+          <t>Cargo only</t>
+        </is>
+      </c>
+      <c r="F117" s="23" t="inlineStr">
+        <is>
+          <t>4 (ISS missions)</t>
+        </is>
+      </c>
+      <c r="G117" s="23" t="inlineStr">
+        <is>
+          <t>3 crew</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>Cargo to ISS (kg)</t>
+        </is>
+      </c>
+      <c r="B118" s="23" t="inlineStr">
+        <is>
+          <t>6,000 (pressurized)</t>
+        </is>
+      </c>
+      <c r="C118" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D118" s="23" t="inlineStr">
+        <is>
+          <t>5,500 (planned)</t>
+        </is>
+      </c>
+      <c r="E118" s="23" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="F118" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G118" s="23" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>NASA Contract Value ($B)</t>
+        </is>
+      </c>
+      <c r="B119" s="23" t="inlineStr">
+        <is>
+          <t>$3.5B (Crew) + Cargo</t>
+        </is>
+      </c>
+      <c r="C119" s="23" t="inlineStr">
+        <is>
+          <t>$4.2B (Crew)</t>
+        </is>
+      </c>
+      <c r="D119" s="23" t="inlineStr">
+        <is>
+          <t>~$1B (Cargo)</t>
+        </is>
+      </c>
+      <c r="E119" s="23" t="inlineStr">
+        <is>
+          <t>~$3B (Cargo)</t>
+        </is>
+      </c>
+      <c r="F119" s="23" t="inlineStr">
+        <is>
+          <t>$1.3B (ISS modules)</t>
+        </is>
+      </c>
+      <c r="G119" s="23" t="inlineStr">
+        <is>
+          <t>n/a (retired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>Cost / Seat (crew, $M)</t>
+        </is>
+      </c>
+      <c r="B120" s="23" t="inlineStr">
+        <is>
+          <t>~$55M</t>
+        </is>
+      </c>
+      <c r="C120" s="23" t="inlineStr">
+        <is>
+          <t>~$90M (est.)</t>
+        </is>
+      </c>
+      <c r="D120" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E120" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F120" s="23" t="inlineStr">
+        <is>
+          <t>$55M (commercial)</t>
+        </is>
+      </c>
+      <c r="G120" s="23" t="inlineStr">
+        <is>
+          <t>$85-90M</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Operational Status</t>
+        </is>
+      </c>
+      <c r="B121" s="23" t="inlineStr">
+        <is>
+          <t>Operational (10+ crew missions)</t>
+        </is>
+      </c>
+      <c r="C121" s="23" t="inlineStr">
+        <is>
+          <t>1 crewed test (issues)</t>
+        </is>
+      </c>
+      <c r="D121" s="23" t="inlineStr">
+        <is>
+          <t>First flight 2025</t>
+        </is>
+      </c>
+      <c r="E121" s="23" t="inlineStr">
+        <is>
+          <t>Operational (cargo)</t>
+        </is>
+      </c>
+      <c r="F121" s="23" t="inlineStr">
+        <is>
+          <t>2 missions completed</t>
+        </is>
+      </c>
+      <c r="G121" s="23" t="inlineStr">
+        <is>
+          <t>Retired (US crew)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>Reliability Track Record</t>
+        </is>
+      </c>
+      <c r="B122" s="23" t="inlineStr">
+        <is>
+          <t>Excellent (100% crew)</t>
+        </is>
+      </c>
+      <c r="C122" s="23" t="inlineStr">
+        <is>
+          <t>Troubled development</t>
+        </is>
+      </c>
+      <c r="D122" s="23" t="inlineStr">
+        <is>
+          <t>Unflown</t>
+        </is>
+      </c>
+      <c r="E122" s="23" t="inlineStr">
+        <is>
+          <t>Good (cargo)</t>
+        </is>
+      </c>
+      <c r="F122" s="23" t="inlineStr">
+        <is>
+          <t>Good (2/2)</t>
+        </is>
+      </c>
+      <c r="G122" s="23" t="inlineStr">
+        <is>
+          <t>Mixed (Soyuz MS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Key Revenue Streams</t>
+        </is>
+      </c>
+      <c r="B123" s="23" t="inlineStr">
+        <is>
+          <t>Crew + cargo + commercial</t>
+        </is>
+      </c>
+      <c r="C123" s="23" t="inlineStr">
+        <is>
+          <t>NASA crew only</t>
+        </is>
+      </c>
+      <c r="D123" s="23" t="inlineStr">
+        <is>
+          <t>NASA cargo</t>
+        </is>
+      </c>
+      <c r="E123" s="23" t="inlineStr">
+        <is>
+          <t>NASA cargo</t>
+        </is>
+      </c>
+      <c r="F123" s="23" t="inlineStr">
+        <is>
+          <t>ISS private + modules</t>
+        </is>
+      </c>
+      <c r="G123" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>GOVERNMENT &amp; OTHER — MARGIN EXPECTATIONS</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n"/>
+      <c r="C125" s="3" t="n"/>
+      <c r="D125" s="3" t="n"/>
+      <c r="E125" s="3" t="n"/>
+      <c r="F125" s="3" t="n"/>
+      <c r="G125" s="3" t="n"/>
+      <c r="H125" s="3" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr"/>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>2022A</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>2023A</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>2024A</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>2025E</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Long-Term Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>Segment Revenue ($M)</t>
+        </is>
+      </c>
+      <c r="B127" s="23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C127" s="23" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D127" s="23" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E127" s="23" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F127" s="23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G127" s="23" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H127" s="23" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NASA Crew Dragon</t>
+        </is>
+      </c>
+      <c r="B128" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="C128" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="D128" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="E128" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="F128" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="G128" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="H128" s="23" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NASA Cargo Dragon</t>
+        </is>
+      </c>
+      <c r="B129" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="C129" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="D129" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="E129" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="F129" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="G129" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H129" s="23" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Commercial Crew (Axiom, etc.)</t>
+        </is>
+      </c>
+      <c r="B130" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="C130" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D130" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="E130" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="F130" s="23" t="n">
+        <v>350</v>
+      </c>
+      <c r="G130" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="H130" s="23" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DOD / NatSec (classified)</t>
+        </is>
+      </c>
+      <c r="B131" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="C131" s="23" t="n">
+        <v>450</v>
+      </c>
+      <c r="D131" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="E131" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="F131" s="23" t="n">
+        <v>600</v>
+      </c>
+      <c r="G131" s="23" t="n">
+        <v>650</v>
+      </c>
+      <c r="H131" s="23" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other government</t>
+        </is>
+      </c>
+      <c r="B132" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="C132" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="D132" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="E132" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="F132" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="G132" s="23" t="n">
+        <v>350</v>
+      </c>
+      <c r="H132" s="23" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>Segment COGS ($M)</t>
+        </is>
+      </c>
+      <c r="B133" s="23" t="n">
+        <v>720</v>
+      </c>
+      <c r="C133" s="23" t="n">
+        <v>770</v>
+      </c>
+      <c r="D133" s="23" t="n">
+        <v>832</v>
+      </c>
+      <c r="E133" s="23" t="n">
+        <v>900</v>
+      </c>
+      <c r="F133" s="23" t="n">
+        <v>960</v>
+      </c>
+      <c r="G133" s="23" t="n">
+        <v>1012</v>
+      </c>
+      <c r="H133" s="23" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dragon vehicle manufacturing</t>
+        </is>
+      </c>
+      <c r="B134" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="C134" s="23" t="n">
+        <v>260</v>
+      </c>
+      <c r="D134" s="23" t="n">
+        <v>270</v>
+      </c>
+      <c r="E134" s="23" t="n">
+        <v>270</v>
+      </c>
+      <c r="F134" s="23" t="n">
+        <v>260</v>
+      </c>
+      <c r="G134" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="H134" s="23" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mission operations &amp; crew support</t>
+        </is>
+      </c>
+      <c r="B135" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="C135" s="23" t="n">
+        <v>220</v>
+      </c>
+      <c r="D135" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="E135" s="23" t="n">
+        <v>280</v>
+      </c>
+      <c r="F135" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="G135" s="23" t="n">
+        <v>320</v>
+      </c>
+      <c r="H135" s="23" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NatSec program costs</t>
+        </is>
+      </c>
+      <c r="B136" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="C136" s="23" t="n">
+        <v>220</v>
+      </c>
+      <c r="D136" s="23" t="n">
+        <v>240</v>
+      </c>
+      <c r="E136" s="23" t="n">
+        <v>270</v>
+      </c>
+      <c r="F136" s="23" t="n">
+        <v>310</v>
+      </c>
+      <c r="G136" s="23" t="n">
+        <v>340</v>
+      </c>
+      <c r="H136" s="23" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other</t>
+        </is>
+      </c>
+      <c r="B137" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="C137" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="D137" s="23" t="n">
+        <v>72</v>
+      </c>
+      <c r="E137" s="23" t="n">
+        <v>80</v>
+      </c>
+      <c r="F137" s="23" t="n">
+        <v>90</v>
+      </c>
+      <c r="G137" s="23" t="n">
+        <v>102</v>
+      </c>
+      <c r="H137" s="23" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="24" t="inlineStr">
+        <is>
+          <t>Segment Gross Profit ($M)</t>
+        </is>
+      </c>
+      <c r="B138" s="25" t="n">
+        <v>480</v>
+      </c>
+      <c r="C138" s="25" t="n">
+        <v>630</v>
+      </c>
+      <c r="D138" s="25" t="n">
+        <v>768</v>
+      </c>
+      <c r="E138" s="25" t="n">
+        <v>900</v>
+      </c>
+      <c r="F138" s="25" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G138" s="25" t="n">
+        <v>1188</v>
+      </c>
+      <c r="H138" s="25" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="24" t="inlineStr">
+        <is>
+          <t>Segment Gross Margin %</t>
+        </is>
+      </c>
+      <c r="B139" s="25" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C139" s="25" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="D139" s="25" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E139" s="25" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="F139" s="25" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G139" s="25" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H139" s="25" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr"/>
+      <c r="B140" s="23" t="inlineStr"/>
+      <c r="C140" s="23" t="inlineStr"/>
+      <c r="D140" s="23" t="inlineStr"/>
+      <c r="E140" s="23" t="inlineStr"/>
+      <c r="F140" s="23" t="inlineStr"/>
+      <c r="G140" s="23" t="inlineStr"/>
+      <c r="H140" s="23" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>Margin Drivers:</t>
+        </is>
+      </c>
+      <c r="B141" s="23" t="inlineStr"/>
+      <c r="C141" s="23" t="inlineStr"/>
+      <c r="D141" s="23" t="inlineStr"/>
+      <c r="E141" s="23" t="inlineStr"/>
+      <c r="F141" s="23" t="inlineStr"/>
+      <c r="G141" s="23" t="inlineStr"/>
+      <c r="H141" s="23" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dragon capsule reuse (flights/capsule)</t>
+        </is>
+      </c>
+      <c r="B142" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C142" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D142" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E142" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F142" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G142" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H142" s="23" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fixed-price vs. cost-plus mix</t>
+        </is>
+      </c>
+      <c r="B143" s="23" t="inlineStr">
+        <is>
+          <t>60/40</t>
+        </is>
+      </c>
+      <c r="C143" s="23" t="inlineStr">
+        <is>
+          <t>65/35</t>
+        </is>
+      </c>
+      <c r="D143" s="23" t="inlineStr">
+        <is>
+          <t>70/30</t>
+        </is>
+      </c>
+      <c r="E143" s="23" t="inlineStr">
+        <is>
+          <t>75/25</t>
+        </is>
+      </c>
+      <c r="F143" s="23" t="inlineStr">
+        <is>
+          <t>75/25</t>
+        </is>
+      </c>
+      <c r="G143" s="23" t="inlineStr">
+        <is>
+          <t>80/20</t>
+        </is>
+      </c>
+      <c r="H143" s="23" t="inlineStr">
+        <is>
+          <t>85/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ISS retirement impact (2030)</t>
+        </is>
+      </c>
+      <c r="B144" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C144" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D144" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E144" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F144" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G144" s="23" t="inlineStr">
+        <is>
+          <t>Transition begins</t>
+        </is>
+      </c>
+      <c r="H144" s="23" t="inlineStr">
+        <is>
+          <t>Post-ISS commercial</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Commercial crew growth rate</t>
+        </is>
+      </c>
+      <c r="B145" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C145" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D145" s="23" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E145" s="23" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="F145" s="23" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G145" s="23" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="H145" s="23" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="26" t="inlineStr">
+        <is>
+          <t>Thesis: Government segment is a stable, high-margin annuity. Dragon reuse + shift to fixed-price contracts drives margin expansion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="26" t="inlineStr">
+        <is>
+          <t>Risk: ISS retirement (2030) creates a gap; offset by commercial space station demand (Axiom, Orbital Reef) and DOD spending growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>CONSOLIDATED SEGMENT MARGIN SUMMARY</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n"/>
+      <c r="C150" s="3" t="n"/>
+      <c r="D150" s="3" t="n"/>
+      <c r="E150" s="3" t="n"/>
+      <c r="F150" s="3" t="n"/>
+      <c r="G150" s="3" t="n"/>
+      <c r="H150" s="3" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>2022A GM%</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>2024A GM%</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>2026E GM%</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>2028E GM%</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>LT Target</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Key Margin Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>Launch Services</t>
+        </is>
+      </c>
+      <c r="B152" s="23" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="C152" s="23" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="D152" s="23" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="E152" s="23" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="F152" s="23" t="inlineStr">
+        <is>
+          <t>68-72%</t>
+        </is>
+      </c>
+      <c r="G152" s="23" t="inlineStr">
+        <is>
+          <t>Booster reuse cadence (amortization)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>Starlink</t>
+        </is>
+      </c>
+      <c r="B153" s="23" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C153" s="23" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D153" s="23" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="E153" s="23" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F153" s="23" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="inlineStr">
+        <is>
+          <t>CPE cost reduction + Starship launch savings</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>Starship</t>
+        </is>
+      </c>
+      <c r="B154" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C154" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D154" s="23" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E154" s="23" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="F154" s="23" t="inlineStr">
+        <is>
+          <t>60-70%</t>
+        </is>
+      </c>
+      <c r="G154" s="23" t="inlineStr">
+        <is>
+          <t>Full vehicle reusability + flight rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>Government &amp; Other</t>
+        </is>
+      </c>
+      <c r="B155" s="23" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C155" s="23" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="D155" s="23" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="E155" s="23" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="F155" s="23" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="G155" s="23" t="inlineStr">
+        <is>
+          <t>Dragon reuse + fixed-price contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr"/>
+      <c r="B156" s="23" t="inlineStr"/>
+      <c r="C156" s="23" t="inlineStr"/>
+      <c r="D156" s="23" t="inlineStr"/>
+      <c r="E156" s="23" t="inlineStr"/>
+      <c r="F156" s="23" t="inlineStr"/>
+      <c r="G156" s="23" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="24" t="inlineStr">
+        <is>
+          <t>Blended Company GM%</t>
+        </is>
+      </c>
+      <c r="B157" s="25" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="C157" s="25" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D157" s="25" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="E157" s="25" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="F157" s="25" t="inlineStr">
+        <is>
+          <t>62-68%</t>
+        </is>
+      </c>
+      <c r="G157" s="25" t="inlineStr">
+        <is>
+          <t>Mix shift toward Starlink (highest scale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>COMPETITIVE MOAT ASSESSMENT</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="n"/>
+      <c r="C160" s="3" t="n"/>
+      <c r="D160" s="3" t="n"/>
+      <c r="E160" s="3" t="n"/>
+      <c r="F160" s="3" t="n"/>
+      <c r="G160" s="3" t="n"/>
+      <c r="H160" s="3" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>Vertical Integration (launch + payload)</t>
+        </is>
+      </c>
+      <c r="B162" s="23" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="C162" s="23" t="inlineStr">
+        <is>
+          <t>10+ years</t>
+        </is>
+      </c>
+      <c r="D162" s="23" t="inlineStr">
+        <is>
+          <t>Only operator that manufactures rockets AND payload (Starlink); eliminates margin stacking</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>Reusability IP</t>
+        </is>
+      </c>
+      <c r="B163" s="23" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="C163" s="23" t="inlineStr">
+        <is>
+          <t>5-10 years</t>
+        </is>
+      </c>
+      <c r="D163" s="23" t="inlineStr">
+        <is>
+          <t>20+ reuses proven; competitors 3-5 years behind on booster recovery alone</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing Scale</t>
+        </is>
+      </c>
+      <c r="B164" s="23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C164" s="23" t="inlineStr">
+        <is>
+          <t>5-8 years</t>
+        </is>
+      </c>
+      <c r="D164" s="23" t="inlineStr">
+        <is>
+          <t>Falcon 9 factory: ~1 booster/month; Starlink: 6 sats/day; drives cost curve advantages</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Cadence &amp; Reliability Track Record</t>
+        </is>
+      </c>
+      <c r="B165" s="23" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="C165" s="23" t="inlineStr">
+        <is>
+          <t>Cumulative</t>
+        </is>
+      </c>
+      <c r="D165" s="23" t="inlineStr">
+        <is>
+          <t>134 launches in 2024; flight heritage reduces insurance costs and wins commercial contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>Spectrum &amp; Orbital Slots (Starlink)</t>
+        </is>
+      </c>
+      <c r="B166" s="23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C166" s="23" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="D166" s="23" t="inlineStr">
+        <is>
+          <t>First-mover ITU filings; Gen2 constellation approved; spectrum is finite</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>Customer Lock-in (Starlink)</t>
+        </is>
+      </c>
+      <c r="B167" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C167" s="23" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D167" s="23" t="inlineStr">
+        <is>
+          <t>CPE investment + service contracts; but low switching costs for consumers vs. fiber</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>Government Relationships</t>
+        </is>
+      </c>
+      <c r="B168" s="23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C168" s="23" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="D168" s="23" t="inlineStr">
+        <is>
+          <t>NASA dependency + growing DOD role; but diversified customer base reduces single-customer risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>Starship Optionality</t>
+        </is>
+      </c>
+      <c r="B169" s="23" t="inlineStr">
+        <is>
+          <t>Transformational</t>
+        </is>
+      </c>
+      <c r="C169" s="23" t="inlineStr">
+        <is>
+          <t>15+ years</t>
+        </is>
+      </c>
+      <c r="D169" s="23" t="inlineStr">
+        <is>
+          <t>If Starship achieves cost targets, it's a platform shift — new markets (point-to-point, space manufacturing)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
